--- a/backend/data/uploads/MES/2026-07-23_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-23_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F933C7CC-536C-43A3-ABB1-D439A2DA4507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D687F46D-B5A8-4864-AE1B-3DC8600A02BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{91A365DA-C415-4C64-AD7F-618D280972CB}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{56EC61AA-72B4-4B88-AD42-96247065C878}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07228DBD-AEB1-4994-B01F-727D287AD05D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB64BCB6-4996-4951-8400-DB3D90EAA393}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
